--- a/output/pdf_financials_xlsx/BN.xlsx
+++ b/output/pdf_financials_xlsx/BN.xlsx
@@ -631,10 +631,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-0.000341</v>
+        <v>0.000871</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.000172</v>
+        <v>0.0021</v>
       </c>
     </row>
     <row r="17">
@@ -691,10 +691,10 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.000641</v>
+        <v>0.001853</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.001307</v>
+        <v>0.003235</v>
       </c>
     </row>
     <row r="21">
@@ -730,10 +730,10 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.000641</v>
+        <v>0.001853</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.001307</v>
+        <v>0.003235</v>
       </c>
     </row>
     <row r="24">
@@ -769,10 +769,10 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>0.003205</v>
+        <v>0.009265000000000001</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>0.002667</v>
+        <v>0.006602</v>
       </c>
     </row>
     <row r="27">
@@ -782,10 +782,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.000341</v>
+        <v>0.000871</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.000172</v>
+        <v>0.0021</v>
       </c>
     </row>
     <row r="28">
@@ -808,10 +808,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.009396</v>
+        <v>0.010608</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.010551</v>
+        <v>0.012479</v>
       </c>
     </row>
     <row r="30">
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>10.92481919866056</v>
+        <v>12.33402320768318</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>14.04926764314248</v>
+        <v>16.61651131824235</v>
       </c>
     </row>
     <row r="31">
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>-287.9765395894428</v>
+        <v>112.743972445465</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>659.8837209302326</v>
+        <v>54.04761904761904</v>
       </c>
     </row>
     <row r="32">
@@ -847,10 +847,10 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>0.7452968397553659</v>
+        <v>2.154500848777992</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>1.74034620505992</v>
+        <v>4.307589880159787</v>
       </c>
     </row>
     <row r="33">
@@ -4216,11 +4216,7 @@
           <t>Shareholders ......................................................................................................................... $</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+      <c r="D83" t="inlineStr"/>
       <c r="E83" s="5" t="n">
         <v>0.000641</v>
       </c>
